--- a/Estimation/Project Plan.xlsx
+++ b/Estimation/Project Plan.xlsx
@@ -310,6 +310,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -328,9 +331,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,13 +654,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
@@ -680,19 +680,19 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="21">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="15">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="17">
         <v>46112</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="17">
         <v>46115</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="16">
         <v>4</v>
       </c>
     </row>
@@ -1046,13 +1046,13 @@
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
@@ -1171,10 +1171,10 @@
       <c r="B34" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="9">
         <f>E24+E32+E33</f>
         <v>59</v>
